--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34F.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIV/LTAIPT_A63F34F.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>48993</t>
   </si>
@@ -121,34 +121,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>F53875FDB006F9D775149E0913A83CC3</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subdirección  de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de enero de 2021 al 31 de marzo de 2021 , el Colegio de Bachilleres del Estado de Tlaxcala, no reporta ningun inmueble como baja.</t>
-  </si>
-  <si>
-    <t>AD348A51F1C789D5FA9DA3559A2B1D05</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de abril de 2022 al 30 de junio de 2022 , el Colegio de Bachilleres del Estado de Tlaxcala, no reporta ningun inmueble como baja.</t>
+    <t>FAA15C03B0CEB18E67C4C985537B25F5</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>no aplica</t>
+  </si>
+  <si>
+    <t>06/07/2023</t>
+  </si>
+  <si>
+    <t>subdirección de planeación y evaluación</t>
+  </si>
+  <si>
+    <t>no hubo bajas en este trimestre</t>
   </si>
 </sst>
 </file>
@@ -541,10 +535,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -555,7 +549,7 @@
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="132.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -736,60 +730,22 @@
         <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
